--- a/New_CenterOfRotation/Finite_COR/Data Files/C45_Data/Model 5 Y_Z Data.xlsx
+++ b/New_CenterOfRotation/Finite_COR/Data Files/C45_Data/Model 5 Y_Z Data.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="23">
   <si>
     <t>Node 25454</t>
   </si>
@@ -75,10 +75,19 @@
     <t>Middle Back Top of C5</t>
   </si>
   <si>
+    <t>Node</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Node </t>
+  </si>
+  <si>
     <t>Initial Coord.</t>
   </si>
   <si>
     <t>X (U1)</t>
+  </si>
+  <si>
+    <t/>
   </si>
 </sst>
 </file>
@@ -165,7 +174,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="general"/>
@@ -200,9 +209,6 @@
     <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -232,6 +238,12 @@
     </xf>
     <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="3" applyFill="1" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="3" applyFill="1" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -541,23 +553,23 @@
     <col min="1" max="1" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="2" max="2" style="11" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="3" max="3" style="11" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="12" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="5" max="5" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="6" max="6" style="11" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="7" max="7" style="11" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="12" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="9" max="9" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="10" max="10" style="11" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="11" max="11" style="11" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="12" max="12" style="12" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="12" max="12" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="13" max="13" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="14" max="14" style="11" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="15" max="15" style="11" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="16" max="16" style="12" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="16" max="16" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="17" max="17" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="18" max="18" style="11" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="19" max="19" style="11" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="20" max="20" style="12" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="20" max="20" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="21" max="21" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="22" max="22" style="11" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="23" max="23" style="11" width="13.576428571428572" customWidth="1" bestFit="1"/>
@@ -1966,23 +1978,23 @@
     <col min="1" max="1" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="2" max="2" style="11" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="3" max="3" style="11" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="12" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="5" max="5" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="6" max="6" style="11" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="7" max="7" style="11" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="12" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="9" max="9" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="10" max="10" style="11" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="11" max="11" style="11" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="12" max="12" style="12" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="12" max="12" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="13" max="13" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="14" max="14" style="11" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="15" max="15" style="11" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="16" max="16" style="12" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="16" max="16" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="17" max="17" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="18" max="18" style="11" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="19" max="19" style="11" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="20" max="20" style="12" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="20" max="20" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="21" max="21" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="22" max="22" style="11" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="23" max="23" style="11" width="13.576428571428572" customWidth="1" bestFit="1"/>
@@ -3392,27 +3404,27 @@
     <col min="2" max="2" style="11" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="3" max="3" style="11" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="4" max="4" style="11" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="12" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="6" max="6" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="7" max="7" style="11" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="8" max="8" style="11" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="9" max="9" style="11" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="10" max="10" style="12" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="10" max="10" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="11" max="11" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="12" max="12" style="11" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="13" max="13" style="11" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="14" max="14" style="11" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="15" max="15" style="12" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="15" max="15" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="16" max="16" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="17" max="17" style="11" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="18" max="18" style="11" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="19" max="19" style="11" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="20" max="20" style="12" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="20" max="20" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="21" max="21" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="22" max="22" style="11" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="23" max="23" style="11" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="24" max="24" style="11" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="25" max="25" style="12" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="25" max="25" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="26" max="26" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="27" max="27" style="11" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="28" max="28" style="11" width="13.576428571428572" customWidth="1" bestFit="1"/>
@@ -3457,167 +3469,179 @@
       <c r="AC1" s="6"/>
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="14"/>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
+      <c r="B2" s="13"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
       <c r="E2" s="4"/>
-      <c r="F2" s="15" t="s">
+      <c r="F2" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="G2" s="14"/>
-      <c r="H2" s="14"/>
-      <c r="I2" s="14"/>
+      <c r="G2" s="13"/>
+      <c r="H2" s="13"/>
+      <c r="I2" s="13"/>
       <c r="J2" s="4"/>
-      <c r="K2" s="13" t="s">
+      <c r="K2" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="L2" s="14"/>
-      <c r="M2" s="14"/>
-      <c r="N2" s="14"/>
+      <c r="L2" s="13"/>
+      <c r="M2" s="13"/>
+      <c r="N2" s="13"/>
       <c r="O2" s="4"/>
-      <c r="P2" s="15" t="s">
+      <c r="P2" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="Q2" s="14"/>
-      <c r="R2" s="14"/>
-      <c r="S2" s="14"/>
+      <c r="Q2" s="13"/>
+      <c r="R2" s="13"/>
+      <c r="S2" s="13"/>
       <c r="T2" s="4"/>
-      <c r="U2" s="13" t="s">
+      <c r="U2" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="V2" s="14"/>
-      <c r="W2" s="14"/>
-      <c r="X2" s="14"/>
+      <c r="V2" s="13"/>
+      <c r="W2" s="13"/>
+      <c r="X2" s="13"/>
       <c r="Y2" s="4"/>
-      <c r="Z2" s="13" t="s">
+      <c r="Z2" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="AA2" s="14"/>
-      <c r="AB2" s="14"/>
-      <c r="AC2" s="14"/>
+      <c r="AA2" s="13"/>
+      <c r="AB2" s="13"/>
+      <c r="AC2" s="13"/>
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
-      <c r="A3" s="16"/>
+      <c r="A3" s="22" t="s">
+        <v>22</v>
+      </c>
       <c r="B3" s="7">
         <v>25454</v>
       </c>
       <c r="C3" s="6"/>
       <c r="D3" s="6"/>
       <c r="E3" s="4"/>
-      <c r="F3" s="16"/>
+      <c r="F3" s="22" t="s">
+        <v>22</v>
+      </c>
       <c r="G3" s="7">
         <v>31067</v>
       </c>
       <c r="H3" s="6"/>
       <c r="I3" s="6"/>
       <c r="J3" s="4"/>
-      <c r="K3" s="16"/>
+      <c r="K3" s="22" t="s">
+        <v>22</v>
+      </c>
       <c r="L3" s="2">
         <v>29005</v>
       </c>
       <c r="M3" s="3"/>
       <c r="N3" s="3"/>
       <c r="O3" s="4"/>
-      <c r="P3" s="16"/>
+      <c r="P3" s="22" t="s">
+        <v>22</v>
+      </c>
       <c r="Q3" s="2">
         <v>45615</v>
       </c>
       <c r="R3" s="3"/>
       <c r="S3" s="3"/>
       <c r="T3" s="4"/>
-      <c r="U3" s="16"/>
+      <c r="U3" s="22" t="s">
+        <v>22</v>
+      </c>
       <c r="V3" s="2">
         <v>52027</v>
       </c>
       <c r="W3" s="3"/>
       <c r="X3" s="3"/>
       <c r="Y3" s="4"/>
-      <c r="Z3" s="17"/>
-      <c r="AA3" s="18">
+      <c r="Z3" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="AA3" s="17">
         <v>49903</v>
       </c>
       <c r="AB3" s="3"/>
       <c r="AC3" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
-      <c r="A4" s="19" t="s">
-        <v>18</v>
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
+      <c r="A4" s="18" t="s">
+        <v>20</v>
       </c>
       <c r="B4" s="8">
         <v>-6.65384</v>
       </c>
-      <c r="C4" s="20">
+      <c r="C4" s="19">
         <v>441.175</v>
       </c>
       <c r="D4" s="8">
         <v>-709.18</v>
       </c>
       <c r="E4" s="4"/>
-      <c r="F4" s="19" t="s">
-        <v>18</v>
+      <c r="F4" s="18" t="s">
+        <v>20</v>
       </c>
       <c r="G4" s="8">
         <v>6.11839</v>
       </c>
-      <c r="H4" s="21">
+      <c r="H4" s="20">
         <v>439.835</v>
       </c>
       <c r="I4" s="8">
         <v>-709.539</v>
       </c>
       <c r="J4" s="4"/>
-      <c r="K4" s="19" t="s">
-        <v>18</v>
+      <c r="K4" s="18" t="s">
+        <v>20</v>
       </c>
       <c r="L4" s="3">
         <v>0.185553</v>
       </c>
-      <c r="M4" s="21">
+      <c r="M4" s="20">
         <v>446.547</v>
       </c>
       <c r="N4" s="3">
         <v>-707.74</v>
       </c>
       <c r="O4" s="4"/>
-      <c r="P4" s="19" t="s">
-        <v>18</v>
+      <c r="P4" s="18" t="s">
+        <v>20</v>
       </c>
       <c r="Q4" s="3">
         <v>-8.27627</v>
       </c>
-      <c r="R4" s="20">
+      <c r="R4" s="19">
         <v>440.046</v>
       </c>
       <c r="S4" s="3">
         <v>-714.179</v>
       </c>
       <c r="T4" s="4"/>
-      <c r="U4" s="19" t="s">
-        <v>18</v>
+      <c r="U4" s="18" t="s">
+        <v>20</v>
       </c>
       <c r="V4" s="3">
         <v>7.72579</v>
       </c>
-      <c r="W4" s="21">
+      <c r="W4" s="20">
         <v>440.224</v>
       </c>
       <c r="X4" s="3">
         <v>-714.622</v>
       </c>
       <c r="Y4" s="4"/>
-      <c r="Z4" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="AA4" s="21">
+      <c r="Z4" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="AA4" s="20">
         <v>-0.0172085</v>
       </c>
-      <c r="AB4" s="20">
+      <c r="AB4" s="19">
         <v>445.307</v>
       </c>
-      <c r="AC4" s="21">
+      <c r="AC4" s="20">
         <v>-714.355</v>
       </c>
     </row>
@@ -3625,8 +3649,8 @@
       <c r="A5" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="22" t="s">
-        <v>19</v>
+      <c r="B5" s="21" t="s">
+        <v>21</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>7</v>
@@ -3638,8 +3662,8 @@
       <c r="F5" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="G5" s="22" t="s">
-        <v>19</v>
+      <c r="G5" s="21" t="s">
+        <v>21</v>
       </c>
       <c r="H5" s="6" t="s">
         <v>7</v>
@@ -3651,8 +3675,8 @@
       <c r="K5" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="L5" s="22" t="s">
-        <v>19</v>
+      <c r="L5" s="21" t="s">
+        <v>21</v>
       </c>
       <c r="M5" s="6" t="s">
         <v>7</v>
@@ -3664,8 +3688,8 @@
       <c r="P5" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="Q5" s="22" t="s">
-        <v>19</v>
+      <c r="Q5" s="21" t="s">
+        <v>21</v>
       </c>
       <c r="R5" s="6" t="s">
         <v>7</v>
@@ -3677,8 +3701,8 @@
       <c r="U5" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="V5" s="22" t="s">
-        <v>19</v>
+      <c r="V5" s="21" t="s">
+        <v>21</v>
       </c>
       <c r="W5" s="6" t="s">
         <v>7</v>
@@ -3690,8 +3714,8 @@
       <c r="Z5" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="AA5" s="22" t="s">
-        <v>19</v>
+      <c r="AA5" s="21" t="s">
+        <v>21</v>
       </c>
       <c r="AB5" s="6" t="s">
         <v>7</v>
@@ -5376,27 +5400,27 @@
     <col min="2" max="2" style="11" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="3" max="3" style="11" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="4" max="4" style="11" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="12" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="6" max="6" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="7" max="7" style="11" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="8" max="8" style="11" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="9" max="9" style="11" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="10" max="10" style="12" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="10" max="10" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="11" max="11" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="12" max="12" style="11" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="13" max="13" style="11" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="14" max="14" style="11" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="15" max="15" style="12" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="15" max="15" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="16" max="16" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="17" max="17" style="11" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="18" max="18" style="11" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="19" max="19" style="11" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="20" max="20" style="12" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="20" max="20" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="21" max="21" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="22" max="22" style="11" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="23" max="23" style="11" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="24" max="24" style="11" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="25" max="25" style="12" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="25" max="25" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="26" max="26" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="27" max="27" style="11" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="28" max="28" style="11" width="13.576428571428572" customWidth="1" bestFit="1"/>
@@ -5441,167 +5465,179 @@
       <c r="AC1" s="6"/>
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="14"/>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
+      <c r="B2" s="13"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
       <c r="E2" s="4"/>
-      <c r="F2" s="15" t="s">
+      <c r="F2" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="G2" s="14"/>
-      <c r="H2" s="14"/>
-      <c r="I2" s="14"/>
+      <c r="G2" s="13"/>
+      <c r="H2" s="13"/>
+      <c r="I2" s="13"/>
       <c r="J2" s="4"/>
-      <c r="K2" s="13" t="s">
+      <c r="K2" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="L2" s="14"/>
-      <c r="M2" s="14"/>
-      <c r="N2" s="14"/>
+      <c r="L2" s="13"/>
+      <c r="M2" s="13"/>
+      <c r="N2" s="13"/>
       <c r="O2" s="4"/>
-      <c r="P2" s="15" t="s">
+      <c r="P2" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="Q2" s="14"/>
-      <c r="R2" s="14"/>
-      <c r="S2" s="14"/>
+      <c r="Q2" s="13"/>
+      <c r="R2" s="13"/>
+      <c r="S2" s="13"/>
       <c r="T2" s="4"/>
-      <c r="U2" s="13" t="s">
+      <c r="U2" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="V2" s="14"/>
-      <c r="W2" s="14"/>
-      <c r="X2" s="14"/>
+      <c r="V2" s="13"/>
+      <c r="W2" s="13"/>
+      <c r="X2" s="13"/>
       <c r="Y2" s="4"/>
-      <c r="Z2" s="13" t="s">
+      <c r="Z2" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="AA2" s="14"/>
-      <c r="AB2" s="14"/>
-      <c r="AC2" s="14"/>
+      <c r="AA2" s="13"/>
+      <c r="AB2" s="13"/>
+      <c r="AC2" s="13"/>
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
-      <c r="A3" s="16"/>
+      <c r="A3" s="15" t="s">
+        <v>18</v>
+      </c>
       <c r="B3" s="7">
         <v>25454</v>
       </c>
       <c r="C3" s="6"/>
       <c r="D3" s="6"/>
       <c r="E3" s="4"/>
-      <c r="F3" s="16"/>
+      <c r="F3" s="15" t="s">
+        <v>18</v>
+      </c>
       <c r="G3" s="7">
         <v>31067</v>
       </c>
       <c r="H3" s="6"/>
       <c r="I3" s="6"/>
       <c r="J3" s="4"/>
-      <c r="K3" s="16"/>
+      <c r="K3" s="15" t="s">
+        <v>18</v>
+      </c>
       <c r="L3" s="2">
         <v>29005</v>
       </c>
       <c r="M3" s="3"/>
       <c r="N3" s="3"/>
       <c r="O3" s="4"/>
-      <c r="P3" s="16"/>
+      <c r="P3" s="15" t="s">
+        <v>18</v>
+      </c>
       <c r="Q3" s="2">
         <v>45615</v>
       </c>
       <c r="R3" s="3"/>
       <c r="S3" s="3"/>
       <c r="T3" s="4"/>
-      <c r="U3" s="16"/>
+      <c r="U3" s="15" t="s">
+        <v>18</v>
+      </c>
       <c r="V3" s="2">
         <v>52027</v>
       </c>
       <c r="W3" s="3"/>
       <c r="X3" s="3"/>
       <c r="Y3" s="4"/>
-      <c r="Z3" s="17"/>
-      <c r="AA3" s="18">
+      <c r="Z3" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="AA3" s="17">
         <v>49903</v>
       </c>
       <c r="AB3" s="3"/>
       <c r="AC3" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
-      <c r="A4" s="19" t="s">
-        <v>18</v>
+      <c r="A4" s="18" t="s">
+        <v>20</v>
       </c>
       <c r="B4" s="8">
         <v>-6.65384</v>
       </c>
-      <c r="C4" s="20">
+      <c r="C4" s="19">
         <v>441.175</v>
       </c>
       <c r="D4" s="8">
         <v>-709.18</v>
       </c>
       <c r="E4" s="4"/>
-      <c r="F4" s="19" t="s">
-        <v>18</v>
+      <c r="F4" s="18" t="s">
+        <v>20</v>
       </c>
       <c r="G4" s="8">
         <v>6.11839</v>
       </c>
-      <c r="H4" s="21">
+      <c r="H4" s="20">
         <v>439.835</v>
       </c>
       <c r="I4" s="8">
         <v>-709.539</v>
       </c>
       <c r="J4" s="4"/>
-      <c r="K4" s="19" t="s">
-        <v>18</v>
+      <c r="K4" s="18" t="s">
+        <v>20</v>
       </c>
       <c r="L4" s="3">
         <v>0.185553</v>
       </c>
-      <c r="M4" s="21">
+      <c r="M4" s="20">
         <v>446.547</v>
       </c>
       <c r="N4" s="3">
         <v>-707.74</v>
       </c>
       <c r="O4" s="4"/>
-      <c r="P4" s="19" t="s">
-        <v>18</v>
+      <c r="P4" s="18" t="s">
+        <v>20</v>
       </c>
       <c r="Q4" s="3">
         <v>-8.27627</v>
       </c>
-      <c r="R4" s="20">
+      <c r="R4" s="19">
         <v>440.046</v>
       </c>
       <c r="S4" s="3">
         <v>-714.179</v>
       </c>
       <c r="T4" s="4"/>
-      <c r="U4" s="19" t="s">
-        <v>18</v>
+      <c r="U4" s="18" t="s">
+        <v>20</v>
       </c>
       <c r="V4" s="3">
         <v>7.72579</v>
       </c>
-      <c r="W4" s="21">
+      <c r="W4" s="20">
         <v>440.224</v>
       </c>
       <c r="X4" s="3">
         <v>-714.622</v>
       </c>
       <c r="Y4" s="4"/>
-      <c r="Z4" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="AA4" s="21">
+      <c r="Z4" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="AA4" s="20">
         <v>-0.0172085</v>
       </c>
-      <c r="AB4" s="20">
+      <c r="AB4" s="19">
         <v>445.307</v>
       </c>
-      <c r="AC4" s="21">
+      <c r="AC4" s="20">
         <v>-714.355</v>
       </c>
     </row>
@@ -5609,8 +5645,8 @@
       <c r="A5" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="22" t="s">
-        <v>19</v>
+      <c r="B5" s="21" t="s">
+        <v>21</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>7</v>
@@ -5622,8 +5658,8 @@
       <c r="F5" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="G5" s="22" t="s">
-        <v>19</v>
+      <c r="G5" s="21" t="s">
+        <v>21</v>
       </c>
       <c r="H5" s="6" t="s">
         <v>7</v>
@@ -5635,8 +5671,8 @@
       <c r="K5" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="L5" s="22" t="s">
-        <v>19</v>
+      <c r="L5" s="21" t="s">
+        <v>21</v>
       </c>
       <c r="M5" s="6" t="s">
         <v>7</v>
@@ -5648,8 +5684,8 @@
       <c r="P5" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="Q5" s="22" t="s">
-        <v>19</v>
+      <c r="Q5" s="21" t="s">
+        <v>21</v>
       </c>
       <c r="R5" s="6" t="s">
         <v>7</v>
@@ -5661,8 +5697,8 @@
       <c r="U5" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="V5" s="22" t="s">
-        <v>19</v>
+      <c r="V5" s="21" t="s">
+        <v>21</v>
       </c>
       <c r="W5" s="6" t="s">
         <v>7</v>
@@ -5674,8 +5710,8 @@
       <c r="Z5" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="AA5" s="22" t="s">
-        <v>19</v>
+      <c r="AA5" s="21" t="s">
+        <v>21</v>
       </c>
       <c r="AB5" s="6" t="s">
         <v>7</v>
@@ -7359,23 +7395,23 @@
     <col min="1" max="1" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="2" max="2" style="11" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="3" max="3" style="11" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="12" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="5" max="5" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="6" max="6" style="11" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="7" max="7" style="11" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="12" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="9" max="9" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="10" max="10" style="11" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="11" max="11" style="11" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="12" max="12" style="12" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="12" max="12" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="13" max="13" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="14" max="14" style="11" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="15" max="15" style="11" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="16" max="16" style="12" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="16" max="16" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="17" max="17" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="18" max="18" style="11" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="19" max="19" style="11" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="20" max="20" style="12" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="20" max="20" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="21" max="21" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="22" max="22" style="11" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="23" max="23" style="11" width="13.576428571428572" customWidth="1" bestFit="1"/>
@@ -8785,23 +8821,23 @@
     <col min="2" max="2" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="3" max="3" style="11" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="4" max="4" style="11" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="12" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="6" max="6" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="7" max="7" style="11" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="8" max="8" style="11" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="12" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="10" max="10" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="11" max="11" style="11" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="12" max="12" style="11" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="13" max="13" style="12" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="13" max="13" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="14" max="14" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="15" max="15" style="11" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="16" max="16" style="11" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="17" max="17" style="12" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="17" max="17" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="18" max="18" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="19" max="19" style="11" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="20" max="20" style="11" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="21" max="21" style="12" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="21" max="21" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="22" max="22" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="23" max="23" style="11" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="24" max="24" style="11" width="13.576428571428572" customWidth="1" bestFit="1"/>
